--- a/SGC-CKN/Excel/b2595155-db60-4142-9cfb-6ad238081c83_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-77_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/b2595155-db60-4142-9cfb-6ad238081c83_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-77_D800_17-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -129,6 +129,9 @@
     <t>4</t>
   </si>
   <si>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+  </si>
+  <si>
     <t xml:space="preserve">05:00
 17/03/2026</t>
   </si>
@@ -136,7 +139,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
     <t xml:space="preserve">05:15
@@ -146,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">06:15
@@ -156,23 +159,13 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:00
-17/03/2026</t>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi. Chiều sâu chọn đầu</t>
   </si>
   <si>
     <t xml:space="preserve">07:16
 17/03/2026</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi. Chiều sâu chọn đầu</t>
-  </si>
-  <si>
     <t xml:space="preserve">07:50
 17/03/2026</t>
   </si>
@@ -180,7 +173,7 @@
     <t>Đạt chiều sâu chọn đầu tại 45m.</t>
   </si>
   <si>
-    <t>9</t>
+    <t>8</t>
   </si>
   <si>
     <t>Sỏi xám vàng, xám xanh TT rất chặt. Kết thúc khoan</t>
@@ -599,7 +592,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -959,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1248,230 +1241,196 @@
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="15" t="s">
+      <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="13">
+      <c r="E14" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="16">
         <v>-18.8</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="16">
         <v>-27.9</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="16">
         <v>0.5</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="16">
         <v>9.1</v>
       </c>
       <c r="J14" s="12">
         <v>18.2</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F15" s="16">
+      <c r="E15" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="19">
         <v>-27.9</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="19">
         <v>-35.1</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="19">
         <v>0.25</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="19">
         <v>7.2</v>
       </c>
       <c r="J15" s="12">
         <v>28.8</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="20" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="19">
+      <c r="E16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="22">
         <v>-35.1</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="22">
         <v>-38.1</v>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="22">
         <v>1</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="22">
         <v>3</v>
       </c>
       <c r="J16" s="8">
         <v>3</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="23" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="22" t="s">
+      <c r="A17" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="24" t="s">
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="D17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="22">
+      <c r="E17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="25">
         <v>-38.1</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="25">
         <v>-45</v>
       </c>
-      <c r="H17" s="22">
-        <v>0.27</v>
-      </c>
-      <c r="I17" s="22">
+      <c r="H17" s="25">
+        <v>0.57</v>
+      </c>
+      <c r="I17" s="25">
         <v>6.9</v>
       </c>
       <c r="J17" s="12">
-        <v>25.87</v>
-      </c>
-      <c r="K17" s="23" t="s">
-        <v>9</v>
+        <v>12.18</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="25">
+      <c r="E18" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="28">
         <v>-45</v>
       </c>
-      <c r="G18" s="25">
-        <v>-51.8</v>
-      </c>
-      <c r="H18" s="25">
-        <v>0.57</v>
-      </c>
-      <c r="I18" s="25">
-        <v>6.8</v>
-      </c>
-      <c r="J18" s="12">
-        <v>12</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="29" t="s">
+      <c r="G18" s="28">
+        <v>-49.4</v>
+      </c>
+      <c r="H18" s="28">
+        <v>2.58</v>
+      </c>
+      <c r="I18" s="28">
+        <v>4.4</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1.7</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" s="30" t="s">
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="28">
-        <v>-51.8</v>
-      </c>
-      <c r="G19" s="28">
-        <v>-56.199999999999996</v>
-      </c>
-      <c r="H19" s="28">
-        <v>2.58</v>
-      </c>
-      <c r="I19" s="28">
-        <v>4.4</v>
-      </c>
-      <c r="J19" s="8">
-        <v>1.7</v>
-      </c>
-      <c r="K19" s="29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-    </row>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1531,7 +1490,6 @@
     <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -1542,7 +1500,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1565,31 +1523,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1661,22 +1619,22 @@
         <v>34</v>
       </c>
       <c r="D4" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="13">
         <v>-13.3</v>
       </c>
       <c r="F4" s="13">
-        <v>-27.9</v>
+        <v>-18.8</v>
       </c>
       <c r="G4" s="13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="13">
-        <v>14.6</v>
+        <v>5.5</v>
       </c>
       <c r="I4" s="12">
-        <v>14.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1687,25 +1645,25 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
       </c>
       <c r="E5" s="16">
+        <v>-18.8</v>
+      </c>
+      <c r="F5" s="16">
         <v>-27.9</v>
       </c>
-      <c r="F5" s="16">
-        <v>-35.1</v>
-      </c>
       <c r="G5" s="16">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="16">
-        <v>7.2</v>
+        <v>9.1</v>
       </c>
       <c r="I5" s="12">
-        <v>28.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1716,25 +1674,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
       </c>
       <c r="E6" s="19">
+        <v>-27.9</v>
+      </c>
+      <c r="F6" s="19">
         <v>-35.1</v>
       </c>
-      <c r="F6" s="19">
-        <v>-38.1</v>
-      </c>
       <c r="G6" s="19">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="H6" s="19">
-        <v>3</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3</v>
+        <v>7.2</v>
+      </c>
+      <c r="I6" s="12">
+        <v>28.8</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1745,25 +1703,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
+        <v>-35.1</v>
+      </c>
+      <c r="F7" s="22">
         <v>-38.1</v>
       </c>
-      <c r="F7" s="22">
-        <v>-45</v>
-      </c>
       <c r="G7" s="22">
-        <v>0.27</v>
+        <v>1</v>
       </c>
       <c r="H7" s="22">
-        <v>6.9</v>
-      </c>
-      <c r="I7" s="12">
-        <v>25.87</v>
+        <v>3</v>
+      </c>
+      <c r="I7" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1774,25 +1732,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
+        <v>-38.1</v>
+      </c>
+      <c r="F8" s="25">
         <v>-45</v>
-      </c>
-      <c r="F8" s="25">
-        <v>-51.8</v>
       </c>
       <c r="G8" s="25">
         <v>0.57</v>
       </c>
       <c r="H8" s="25">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I8" s="12">
-        <v>12</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1803,16 +1761,16 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-51.8</v>
+        <v>-45</v>
       </c>
       <c r="F9" s="28">
-        <v>-56.2</v>
+        <v>-49.4</v>
       </c>
       <c r="G9" s="28">
         <v>2.58</v>
@@ -1826,7 +1784,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>9</v>
@@ -1835,22 +1793,22 @@
         <v>9</v>
       </c>
       <c r="D10" s="33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="33">
         <v>-1.2</v>
       </c>
       <c r="F10" s="33">
-        <v>-56.2</v>
+        <v>-49.4</v>
       </c>
       <c r="G10" s="33">
-        <v>6.67</v>
+        <v>6.4</v>
       </c>
       <c r="H10" s="33">
-        <v>55</v>
+        <v>48.2</v>
       </c>
       <c r="I10" s="33">
-        <v>8.25</v>
+        <v>7.53</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/b2595155-db60-4142-9cfb-6ad238081c83_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-77_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/b2595155-db60-4142-9cfb-6ad238081c83_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-77_D800_17-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>17-77</t>
+    <t>P11-74</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/b2595155-db60-4142-9cfb-6ad238081c83_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-77_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/b2595155-db60-4142-9cfb-6ad238081c83_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-77_D800_17-03-2026.xlsx
@@ -17,7 +17,7 @@
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P11-74</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGC-KCN0002</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">03:00
@@ -106,10 +106,13 @@
 17/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">04:00
@@ -119,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét- đồi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">04:30
@@ -139,9 +142,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
-  </si>
-  <si>
     <t xml:space="preserve">05:15
 17/03/2026</t>
   </si>
@@ -149,7 +149,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">06:15
@@ -159,7 +159,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi. Chiều sâu chọn đầu</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">07:16
@@ -176,7 +176,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt. Kết thúc khoan</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:25
@@ -1167,24 +1167,24 @@
         <v>3</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-2.7</v>
@@ -1202,24 +1202,24 @@
         <v>21.2</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-13.3</v>
@@ -1237,24 +1237,24 @@
         <v>11</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-18.8</v>
@@ -1272,21 +1272,21 @@
         <v>18.2</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>41</v>
@@ -1307,7 +1307,7 @@
         <v>28.8</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1342,7 +1342,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1587,7 +1587,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1616,7 +1616,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1674,7 +1674,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1787,10 +1787,10 @@
         <v>63</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="33">
         <v>8</v>
